--- a/docs/sistema_funcional/Levantamiento para costear - adoOps.xlsx
+++ b/docs/sistema_funcional/Levantamiento para costear - adoOps.xlsx
@@ -8,17 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="adoOps" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 · Ecosistema TI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1 · Tecnología" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2 · Usuarios y volumen" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3 · Caso de negocio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3 · Cómo se hace hoy" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1 · Ecosistema TI'!$A$5:$G$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 · Ecosistema TI'!$5:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 · Usuarios y volumen'!$A$5:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1 · Tecnología'!$A$5:$G$38</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 · Tecnología'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 · Usuarios y volumen'!$A$5:$G$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2 · Usuarios y volumen'!$5:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 · Caso de negocio'!$A$5:$G$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 · Caso de negocio'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 · Cómo se hace hoy'!$A$5:$G$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 · Cómo se hace hoy'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -115,9 +115,8 @@
     </font>
     <font>
       <name val="Aptos"/>
-      <i val="1"/>
       <color rgb="FF43566A"/>
-      <sz val="9.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -244,7 +243,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +258,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -690,114 +689,114 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Las preguntas están hechas sobre lo que este sistema realmente usa, no sobre una lista genérica: cada una corresponde a una pieza que hoy funciona y que habría que resolver de otra forma dentro de su ecosistema.</t>
+          <t>Necesitamos entender cómo funciona hoy su infraestructura y su operación para dimensionar bien las dos alternativas: mantener el sistema como servicio mensual, o instalarlo en sus servidores.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Cómo usarlo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+          <t>Cómo completarlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Una hoja por bloque. Las responde gente distinta y ninguno necesita esperar a los otros: el primero lo contesta TI, el segundo y el tercero jefatura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Las 15 preguntas marcadas «Mueve el número» son las que cambian la estimación de forma material. Sin ellas cualquier cifra sería inventada. Si el tiempo alcanza para poco, esas primero; el resto afina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Escriban en la columna Respuesta. Si algo no se sabe todavía, dejarlo en blanco es más útil que aproximar: un supuesto que nadie marcó como supuesto termina dentro del precio.</t>
+          <t>Tres hojas, una por tema. Las responde gente distinta y ninguna necesita esperar a las otras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Escriban en la columna Respuesta. Si algo no lo saben todavía, déjenlo en blanco: es más útil que una aproximación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Las preguntas marcadas «Necesario para costear» son las que pueden cambiar el alcance o el esfuerzo. Las demás ayudan a diseñar mejor, pero no bloquean una primera estimación.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Las siete piezas que habría que resolver adentro</t>
+          <t>Qué habría que definir si va a sus servidores</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>HOY FUNCIONA CON</t>
+          <t>CÓMO FUNCIONA HOY</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>ADENTRO HABRÍA QUE RESOLVERLO CON</t>
+          <t>QUÉ HABRÍA QUE DEFINIR</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Node.js sobre Vercel</t>
+          <t>Aplicación web sobre Node.js</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Un servidor o contenedor que ejecute Node</t>
+          <t>Dónde se instala y quién la opera</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Base de datos PostgreSQL</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>PostgreSQL propio, o portar a SQL Server</t>
+          <t>Qué motor usan ustedes</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Almacenamiento de archivos en la nube</t>
+          <t>Archivos en almacenamiento en la nube</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Recurso compartido, Azure Blob o similar</t>
+          <t>Dónde guardar fotos y PDF</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Transcripción y extracción con IA</t>
+          <t>Transcripción y lectura del audio con IA</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Azure OpenAI, o salida a internet</t>
+          <t>Qué servicio de IA usar y desde dónde</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>WhatsApp vía un proveedor</t>
+          <t>WhatsApp a través de un proveedor</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>WhatsApp Business API — no existe en local</t>
+          <t>Qué número usar y bajo qué cuenta</t>
         </is>
       </c>
     </row>
@@ -809,19 +808,19 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Entra ID, si quieren inicio de sesión único</t>
+          <t>Si prefieren cuenta corporativa</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Maestra cargada desde Excel</t>
+          <t>Agricultores y lotes cargados desde Excel</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Integración con el SIA</t>
+          <t>Cómo conectarlo al SIA</t>
         </is>
       </c>
     </row>
@@ -835,9 +834,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -859,14 +858,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
@@ -874,21 +873,21 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>1 · Ecosistema TI</t>
+          <t>1 · Tecnología</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>RESPONDE: TECNOLOGÍA / TI</t>
+          <t>RESPONDE: TI</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Qué tan lejos está lo que hoy funciona de lo que ustedes operan. De acá sale el costo de migrar y el de mantenerlo después.</t>
+          <t>Cómo funciona hoy su infraestructura, para saber qué implicaría instalar el sistema en sus servidores.</t>
         </is>
       </c>
     </row>
@@ -910,7 +909,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Por qué lo preguntamos</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -929,28 +928,28 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="76" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Dónde se ejecuta</t>
+          <t>Servidores</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>¿Los servidores son físicos en sus oficinas, máquinas virtuales en su datacenter, o tienen ya suscripción de Azure con cargas productivas?</t>
+          <t>¿Dónde correrían una aplicación web como esta?</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Cambia por completo el trabajo: publicar en Azure App Service se parece a lo que ya está; un servidor físico en oficina agrega red, certificados, respaldos y monitoreo que hoy no existen.</t>
+          <t>Servidores propios, máquinas virtuales, Azure u otro.</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -962,87 +961,99 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Dónde se ejecuta</t>
+          <t>Servidores</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>¿Corren contenedores hoy (Docker, Kubernetes) o despliegan aplicaciones directo sobre el sistema operativo?</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr"/>
-      <c r="E7" s="26" t="inlineStr"/>
+          <t>¿Usan contenedores o instalan las aplicaciones directo en el servidor?</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes u otro.</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F7" s="21" t="inlineStr"/>
       <c r="G7" s="21" t="inlineStr"/>
     </row>
-    <row r="8" ht="61" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Dónde se ejecuta</t>
+          <t>Servidores</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>¿Qué sistema operativo y qué versión de Node.js tienen disponible? ¿Pueden instalar una versión distinta si hace falta?</t>
+          <t>¿Qué sistema operativo usan en esos servidores?</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr"/>
-      <c r="E8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr"/>
       <c r="G8" s="21" t="inlineStr"/>
     </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="16" t="n">
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Dónde se ejecuta</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>El sistema tiene que ser alcanzable desde internet para recibir los mensajes de WhatsApp. ¿Cómo publican hoy una aplicación hacia afuera, y qué exige pasar por seguridad?</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>WhatsApp le avisa al sistema mediante una llamada entrante desde internet. Si la política es que nada se publica hacia afuera, hay que diseñar un intermediario, y eso es trabajo, no configuración.</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Mueve el número</t>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Servidores</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>¿Pueden instalar Node.js, o ya lo tienen disponible?</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Si ya lo tienen, indicar la versión.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
       <c r="G9" s="21" t="inlineStr"/>
     </row>
-    <row r="10" ht="76" customHeight="1">
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Servidores</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>¿Tienen PostgreSQL en producción, o su motor estándar es SQL Server?</t>
+          <t>¿Cómo publican hoy una aplicación para que sea accesible desde internet?</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Es la pregunta más cara del cuestionario. Con PostgreSQL, mover la base es cuestión de horas. Con SQL Server hay que reescribir toda la capa de datos y volver a probarla entera.</t>
+          <t>El sistema recibe los mensajes de WhatsApp por una llamada entrante, así que necesita una dirección pública.</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -1054,242 +1065,270 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Servidores</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>¿Quién administra las bases: un equipo interno, un proveedor, o el mismo equipo de desarrollo?</t>
+          <t>¿Qué revisiones o autorizaciones piden para publicar algo hacia afuera?</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr"/>
-      <c r="E11" s="26" t="inlineStr"/>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F11" s="21" t="inlineStr"/>
       <c r="G11" s="21" t="inlineStr"/>
     </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="27" t="n">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Base de datos</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>¿Qué política de respaldo y de recuperación aplican a un sistema como este?</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="inlineStr"/>
-      <c r="E12" s="31" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>¿Qué motor de base de datos usan?</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>SQL Server, PostgreSQL, Oracle u otro.</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Necesario para costear</t>
+        </is>
+      </c>
       <c r="F12" s="21" t="inlineStr"/>
       <c r="G12" s="21" t="inlineStr"/>
     </row>
-    <row r="13" ht="61" customHeight="1">
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="22" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Fotos y PDF</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>¿Dónde guardarían archivos que la aplicación escribe sola: un recurso compartido de red, Azure Blob Storage, SharePoint?</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr"/>
-      <c r="E13" s="26" t="inlineStr"/>
+          <t>¿Quién administra las bases de datos?</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Equipo interno, proveedor externo, el mismo equipo de desarrollo.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F13" s="21" t="inlineStr"/>
       <c r="G13" s="21" t="inlineStr"/>
     </row>
-    <row r="14" ht="46" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="27" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
-          <t>Fotos y PDF</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
-          <t>Cada visita puede traer tres fotos de teléfono. ¿Hay límite de espacio, o política de cuánto tiempo se conservan?</t>
+          <t>¿Qué política de respaldos aplican a un sistema como este?</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr"/>
-      <c r="E14" s="31" t="inlineStr"/>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="inlineStr"/>
       <c r="G14" s="21" t="inlineStr"/>
     </row>
-    <row r="15" ht="91" customHeight="1">
-      <c r="A15" s="16" t="n">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Inteligencia artificial</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>¿Tienen Azure OpenAI Service habilitado, o alguna política sobre qué modelos de IA se pueden usar y en qué región deben quedar los datos?</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>La segunda pregunta más cara. Si Azure OpenAI está disponible, se cambia una configuración. Si no, hay que decidir entre pedir una excepción para salir a internet o buscar otro camino, y todo el sistema depende de que la transcripción funcione.</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>Mueve el número</t>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Archivos</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>¿Dónde guardan hoy los archivos que genera una aplicación?</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Carpeta de red, Azure Blob, SharePoint u otro.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
       <c r="G15" s="21" t="inlineStr"/>
     </row>
-    <row r="16" ht="61" customHeight="1">
-      <c r="A16" s="16" t="n">
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Inteligencia artificial</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>¿Hay algo que impida que el audio de un zonal y el nombre de un agricultor salgan de la red de la empresa para ser procesados?</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Es exactamente lo que ocurre hoy, y hay que saber si es aceptable o si es la razón por la que quieren llevarlo adentro.</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>Mueve el número</t>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Archivos</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>¿Hay límite de espacio o tiempo de conservación?</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>Cada visita puede traer tres fotos de teléfono.</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
       <c r="G16" s="21" t="inlineStr"/>
     </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="22" t="n">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Inteligencia artificial</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>Si un modelo mejor apareciera en seis meses, ¿quién decide si se cambia y cuánto tarda esa aprobación?</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr"/>
-      <c r="E17" s="26" t="inlineStr"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>¿Tienen Azure OpenAI habilitado?</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Necesario para costear</t>
+        </is>
+      </c>
       <c r="F17" s="21" t="inlineStr"/>
       <c r="G17" s="21" t="inlineStr"/>
     </row>
-    <row r="18" ht="76" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>¿El número que se use debe ser corporativo? ¿Tienen ya una cuenta de WhatsApp Business verificada a nombre de la empresa?</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>WhatsApp no se puede alojar en un servidor propio: siempre pasa por Meta o por un proveedor. Es la única pieza que no se puede llevar adentro, y conviene decirlo antes de que aparezca como sorpresa.</t>
-        </is>
-      </c>
+          <t>¿Hay política sobre qué modelos de IA se pueden usar?</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr"/>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
       <c r="G18" s="21" t="inlineStr"/>
     </row>
-    <row r="19" ht="46" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="22" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>¿Existe alguna restricción sobre usar WhatsApp para comunicaciones de la empresa?</t>
+          <t>¿Los datos deben quedar en alguna región en particular?</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr"/>
-      <c r="E19" s="26" t="inlineStr"/>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F19" s="21" t="inlineStr"/>
       <c r="G19" s="21" t="inlineStr"/>
     </row>
-    <row r="20" ht="61" customHeight="1">
+    <row r="20" ht="46" customHeight="1">
       <c r="A20" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Identidad y acceso</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>¿Quieren que la gente entre con su cuenta corporativa de Microsoft, o está bien un usuario y contraseña propios del sistema?</t>
+          <t>¿Pueden salir datos de la empresa hacia un servicio externo para ser procesados?</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>Inicio de sesión único con Entra ID es lo que van a pedir tarde o temprano, y es trabajo concreto. Saberlo ahora evita construirlo dos veces.</t>
+          <t>Hoy el audio del zonal y el nombre del agricultor se procesan fuera de la red.</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
       <c r="G20" s="21" t="inlineStr"/>
     </row>
-    <row r="21" ht="46" customHeight="1">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="22" t="n">
         <v>16</v>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Identidad y acceso</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>¿Los zonales tienen cuenta corporativa y la usan a diario desde el teléfono?</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>Si no la usan, el inicio de sesión único agrega fricción justo a quien menos tolera fricción.</t>
-        </is>
-      </c>
-      <c r="E21" s="26" t="inlineStr"/>
+          <t>¿Quién autoriza cambiar de modelo, y cuánto suele demorar?</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr"/>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F21" s="21" t="inlineStr"/>
       <c r="G21" s="21" t="inlineStr"/>
     </row>
@@ -1299,41 +1338,45 @@
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
-          <t>Identidad y acceso</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="C22" s="29" t="inlineStr">
         <is>
-          <t>¿Hay exigencia de segundo factor para sistemas internos?</t>
+          <t>¿El número debe ser corporativo?</t>
         </is>
       </c>
       <c r="D22" s="30" t="inlineStr"/>
-      <c r="E22" s="31" t="inlineStr"/>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F22" s="21" t="inlineStr"/>
       <c r="G22" s="21" t="inlineStr"/>
     </row>
-    <row r="23" ht="76" customHeight="1">
+    <row r="23" ht="46" customHeight="1">
       <c r="A23" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Integración con el SIA</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>¿El SIA expone una API, una base consultable, o solo permite exportar a Excel?</t>
+          <t>¿Tienen una cuenta de WhatsApp Business verificada a nombre de la empresa?</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>Decide si los agricultores y lotes se sincronizan solos o si alguien va a cargar un archivo cada temporada. Una carga manual que se olvida es un sistema que se desactualiza sin avisar.</t>
+          <t>WhatsApp siempre pasa por Meta o por un proveedor: no se puede instalar en un servidor propio.</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr"/>
@@ -1345,143 +1388,367 @@
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>Integración con el SIA</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="C24" s="29" t="inlineStr">
         <is>
-          <t>¿Quién lo mantiene: equipo interno o un proveedor? ¿Cuánto tarda una solicitud de cambio ahí?</t>
+          <t>¿Hay restricciones internas para usar WhatsApp en comunicaciones de la empresa?</t>
         </is>
       </c>
       <c r="D24" s="30" t="inlineStr"/>
-      <c r="E24" s="31" t="inlineStr"/>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F24" s="21" t="inlineStr"/>
       <c r="G24" s="21" t="inlineStr"/>
     </row>
     <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="22" t="n">
+      <c r="A25" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>Integración con el SIA</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>¿Debería la visita escribirse de vuelta en el SIA, o basta con que viva en este sistema?</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr"/>
-      <c r="E25" s="26" t="inlineStr"/>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Usuarios y accesos</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>¿Prefieren que entren con su cuenta de Microsoft o con un usuario propio del sistema?</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Hoy el sistema usa usuario y contraseña propios.</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Necesario para costear</t>
+        </is>
+      </c>
       <c r="F25" s="21" t="inlineStr"/>
       <c r="G25" s="21" t="inlineStr"/>
     </row>
-    <row r="26" ht="61" customHeight="1">
-      <c r="A26" s="16" t="n">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Una vez instalado, ¿quién lo opera y lo mantiene: su equipo, nosotros, o compartido?</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>Determina la mitad del costo, y es la pregunta que más se posterga. Un sistema sin dueño declarado se cae un sábado y nadie sabe a quién llamar.</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Mueve el número</t>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>Usuarios y accesos</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>¿Los zonales tienen cuenta corporativa y la usan desde el teléfono?</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr"/>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
       <c r="G26" s="21" t="inlineStr"/>
     </row>
-    <row r="27" ht="46" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="22" t="n">
         <v>22</v>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Usuarios y accesos</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>¿Tienen mesa de ayuda? ¿Qué esperarían que ocurra si un zonal manda un audio y no le llega respuesta?</t>
+          <t>¿Exigen segundo factor para sistemas internos?</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr"/>
-      <c r="E27" s="26" t="inlineStr"/>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F27" s="21" t="inlineStr"/>
       <c r="G27" s="21" t="inlineStr"/>
     </row>
-    <row r="28" ht="61" customHeight="1">
-      <c r="A28" s="27" t="n">
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="28" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>¿Qué exigen para poner un sistema en producción: pruebas, documentación, revisión de seguridad, ambiente de pruebas separado?</t>
-        </is>
-      </c>
-      <c r="D28" s="30" t="inlineStr"/>
-      <c r="E28" s="31" t="inlineStr"/>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Integración con el SIA</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>¿El SIA tiene API, base consultable, o solo permite exportar a Excel?</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Hoy los agricultores y lotes se cargan desde un Excel exportado.</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Necesario para costear</t>
+        </is>
+      </c>
       <c r="F28" s="21" t="inlineStr"/>
       <c r="G28" s="21" t="inlineStr"/>
     </row>
-    <row r="29" ht="76" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="22" t="n">
         <v>24</v>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Datos personales</t>
+          <t>Integración con el SIA</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>El sistema guarda nombre, teléfono y observaciones sobre el campo de agricultores, que son personas naturales. ¿Tienen política de tratamiento de datos personales que debamos cumplir?</t>
+          <t>¿Quién mantiene el SIA?</t>
         </is>
       </c>
       <c r="D29" s="25" t="inlineStr"/>
-      <c r="E29" s="26" t="inlineStr"/>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F29" s="21" t="inlineStr"/>
       <c r="G29" s="21" t="inlineStr"/>
     </row>
-    <row r="30" ht="46" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="27" t="n">
         <v>25</v>
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Datos personales</t>
+          <t>Integración con el SIA</t>
         </is>
       </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>¿Cuánto tiempo debe conservarse el historial de un agricultor, y qué pasa cuando termina el contrato?</t>
+          <t>¿Cuánto suele demorar una solicitud de cambio ahí?</t>
         </is>
       </c>
       <c r="D30" s="30" t="inlineStr"/>
-      <c r="E30" s="31" t="inlineStr"/>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F30" s="21" t="inlineStr"/>
       <c r="G30" s="21" t="inlineStr"/>
     </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Integración con el SIA</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>¿Necesitan que la visita quede registrada también en el SIA?</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr"/>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr"/>
+      <c r="G31" s="21" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Soporte y operación</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>¿Quién operaría el sistema una vez instalado?</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Su equipo, nosotros, o compartido.</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Necesario para costear</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr"/>
+      <c r="G32" s="21" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Soporte y operación</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>¿Tienen mesa de ayuda?</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr"/>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr"/>
+      <c r="G33" s="21" t="inlineStr"/>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>Soporte y operación</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>Si un zonal manda un audio y no recibe respuesta, ¿a quién debería avisar?</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr"/>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr"/>
+      <c r="G34" s="21" t="inlineStr"/>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Soporte y operación</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>¿Qué piden para poner un sistema en producción?</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>Pruebas, documentación, revisión de seguridad, ambiente de pruebas separado.</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr"/>
+      <c r="G35" s="21" t="inlineStr"/>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Datos personales</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>¿Tienen política de tratamiento de datos personales que debamos cumplir?</t>
+        </is>
+      </c>
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>El sistema guarda nombre, teléfono y observaciones del campo de cada agricultor.</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr"/>
+      <c r="G36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37" ht="46" customHeight="1">
+      <c r="A37" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Datos personales</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo debe conservarse el historial de un agricultor?</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr"/>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr"/>
+      <c r="G37" s="21" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>Datos personales</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>¿Qué pasa con esos datos cuando termina el contrato?</t>
+        </is>
+      </c>
+      <c r="D38" s="30" t="inlineStr"/>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr"/>
+      <c r="G38" s="21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:G30"/>
+  <autoFilter ref="A5:G38"/>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
@@ -1506,14 +1773,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1535,7 +1802,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Para poder proponer un precio si se queda como servicio mensual, y para dimensionar la infraestructura si se va adentro.</t>
+          <t>Cuánta gente lo usaría y con qué frecuencia.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1824,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Por qué lo preguntamos</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1576,28 +1843,24 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="61" customHeight="1">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Las personas</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>¿Cuántos zonales y supervisores hay hoy en total, contando las dos áreas?</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Es la base de cualquier precio por usuario. Hoy el sistema conoce tres nombres de las planillas; cuántos son de verdad no lo sabemos.</t>
-        </is>
-      </c>
+          <t>¿Cuántos zonales y supervisores hay en total, sumando las dos áreas?</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr"/>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -1609,7 +1872,7 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Las personas</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -1618,70 +1881,82 @@
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr"/>
-      <c r="E7" s="26" t="inlineStr"/>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F7" s="21" t="inlineStr"/>
       <c r="G7" s="21" t="inlineStr"/>
     </row>
-    <row r="8" ht="61" customHeight="1">
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Las personas</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>¿Hay otras áreas o filiales del grupo que hagan visitas a campo y podrían usar esto? En la primera reunión se mencionó Confarm.</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="inlineStr"/>
-      <c r="E8" s="31" t="inlineStr"/>
+          <t>¿Hay otras áreas o empresas del grupo que hagan visitas a campo?</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>En la primera reunión se mencionó Confarm.</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr"/>
       <c r="G8" s="21" t="inlineStr"/>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="22" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Las personas</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>¿Cuántos agricultores tienen bajo contrato en total, sumando las áreas?</t>
+          <t>¿Cuántos agricultores tienen bajo contrato?</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr"/>
-      <c r="E9" s="26" t="inlineStr"/>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F9" s="21" t="inlineStr"/>
       <c r="G9" s="21" t="inlineStr"/>
     </row>
-    <row r="10" ht="61" customHeight="1">
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>El volumen</t>
+          <t>Volumen</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>¿Cuántas visitas a campo hace un zonal en una semana típica de temporada alta?</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Define el costo variable (cada visita consume transcripción y extracción) y es también el numerador del caso de negocio.</t>
-        </is>
-      </c>
+          <t>¿Cuántas visitas a campo hace un zonal en una semana de temporada alta?</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -1693,7 +1968,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>El volumen</t>
+          <t>Volumen</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -1702,39 +1977,62 @@
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr"/>
-      <c r="E11" s="26" t="inlineStr"/>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F11" s="21" t="inlineStr"/>
       <c r="G11" s="21" t="inlineStr"/>
     </row>
-    <row r="12" ht="76" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>El volumen</t>
+          <t>Volumen</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>¿En qué meses del año se concentra el trabajo de terreno, y cuántos meses queda prácticamente detenido?</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>La agricultura es estacional y el software normalmente no. Un precio mensual plano por doce meses para un sistema que se usa cinco es una discusión que conviene tener ahora y no en la primera renovación.</t>
-        </is>
-      </c>
+          <t>¿En qué meses se concentra el trabajo de terreno?</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr"/>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
       <c r="G12" s="21" t="inlineStr"/>
     </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>¿Cuántos meses al año queda prácticamente detenido?</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr"/>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:G12"/>
+  <autoFilter ref="A5:G13"/>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
@@ -1759,14 +2057,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1774,7 +2072,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>3 · Caso de negocio</t>
+          <t>3 · Cómo se hace hoy</t>
         </is>
       </c>
     </row>
@@ -1788,7 +2086,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Lo que hoy cuesta hacerlo a mano. Sin estas cifras el precio queda sin contra qué medirse, y cualquier número parece caro.</t>
+          <t>Cómo funciona hoy el registro de las visitas, para poder comparar.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +2108,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Por qué lo preguntamos</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1829,55 +2127,47 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="76" customHeight="1">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>El tiempo que se va hoy</t>
+          <t>Registrar una visita</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Después de recorrer un campo, ¿cuánto tarda hoy un zonal en dejar registrado lo que vio? ¿Y cuántas veces no alcanza a hacerlo?</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Es el corazón del caso de negocio. En la primera reunión se estimó que alrededor de la mitad de las visitas queda respaldada solo por WhatsApp, y de esa mitad nada queda consultable.</t>
-        </is>
-      </c>
+          <t>Después de recorrer un campo, ¿cuánto tarda un zonal en dejar registrado lo que vio?</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr"/>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
       <c r="G6" s="21" t="inlineStr"/>
     </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="16" t="n">
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>El tiempo que se va hoy</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>El informe mensual al cliente en el extranjero: ¿cuántas horas toma armarlo, quién lo hace y cuántos se emiten al año?</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>Es la tarea más medible de todas. Bajar fotos de los teléfonos, ordenarlas en Drive por agricultor y fecha, y pegarlas una a una en un PowerPoint tiene un número de horas concreto detrás.</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Mueve el número</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Registrar una visita</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>¿Con qué frecuencia no alcanza a registrarlo?</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr"/>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -1889,128 +2179,209 @@
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>El tiempo que se va hoy</t>
+          <t>Registrar una visita</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>¿Cuánto tiempo se pierde buscando en conversaciones de WhatsApp qué se conversó con un agricultor?</t>
+          <t>¿Cuánto tiempo toma buscar en WhatsApp qué se conversó con un agricultor?</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr"/>
-      <c r="E8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr"/>
       <c r="G8" s="21" t="inlineStr"/>
     </row>
-    <row r="9" ht="61" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Lo que cuesta no tener el registro</t>
+          <t>Informe mensual al cliente</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>¿Cuántas veces al año hay una discusión con un agricultor sobre lo que se hizo o no se hizo en su campo, y cómo terminan?</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Es el valor que nadie contabiliza. Cuando a un agricultor le va mal y no recuerda haber hecho algo mal, la trazabilidad es la diferencia entre una conversación y un problema.</t>
-        </is>
-      </c>
+          <t>¿Cuántas horas toma armar el informe mensual?</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>Mueve el número</t>
+          <t>Necesario para costear</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
       <c r="G9" s="21" t="inlineStr"/>
     </row>
-    <row r="10" ht="46" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Lo que cuesta no tener el registro</t>
+          <t>Informe mensual al cliente</t>
         </is>
       </c>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>¿Ha habido pérdidas de producción que se hubieran evitado detectando antes un problema de riego, maleza o sanidad?</t>
+          <t>¿Quién lo arma y cuántos se emiten al año?</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr"/>
-      <c r="E10" s="31" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F10" s="21" t="inlineStr"/>
       <c r="G10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Lo que cuesta no tener el registro</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>Cuando un zonal deja la empresa, ¿qué pasa con lo que sabía de sus campos?</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr"/>
-      <c r="E11" s="26" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Trazabilidad</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>¿Cuántas veces al año hay una discusión con un agricultor sobre lo que se hizo en su campo?</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Necesario para costear</t>
+        </is>
+      </c>
       <c r="F11" s="21" t="inlineStr"/>
       <c r="G11" s="21" t="inlineStr"/>
     </row>
-    <row r="12" ht="61" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="27" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>Lo que valdría ganar</t>
+          <t>Trazabilidad</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
         <is>
-          <t>Si el próximo año pudieran ver la nota agronómica de cada lote a lo largo de la temporada, ¿qué decisión tomarían con eso que hoy no pueden tomar?</t>
+          <t>¿Cómo se resuelven hoy esas situaciones?</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr"/>
-      <c r="E12" s="31" t="inlineStr"/>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F12" s="21" t="inlineStr"/>
       <c r="G12" s="21" t="inlineStr"/>
     </row>
-    <row r="13" ht="61" customHeight="1">
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="22" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Lo que valdría ganar</t>
+          <t>Trazabilidad</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>¿Qué tendría que pasar en los próximos tres meses para que esto se considere un éxito y valga la pena seguir?</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>Vale más que cualquier respuesta técnica: si no hay acuerdo sobre qué es el éxito, el mejor sistema posible se evalúa contra expectativas distintas.</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="inlineStr"/>
+          <t>¿Ha habido pérdidas de producción que se hubieran evitado detectando antes un problema de riego, maleza o sanidad?</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr"/>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
       <c r="F13" s="21" t="inlineStr"/>
       <c r="G13" s="21" t="inlineStr"/>
     </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Trazabilidad</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Cuando un zonal deja la empresa, ¿qué pasa con lo que sabía de sus campos?</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr"/>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Qué esperan</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Si pudieran ver la nota agronómica de cada lote a lo largo de la temporada, ¿qué harían con esa información?</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr"/>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Qué esperan</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>¿Qué tendría que pasar en los próximos tres meses para que valga la pena seguir?</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr"/>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:G13"/>
+  <autoFilter ref="A5:G16"/>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
